--- a/education_forms/044_filipino_composers_knowledge_quiz--education_forms.xlsx
+++ b/education_forms/044_filipino_composers_knowledge_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>composer_century</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Question</t>
+          <t>What century did the composer work in?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name_of_composer</t>
+          <t>composer_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Name Of Composer</t>
+          <t>What is the name of the composer?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>century_of_composers</t>
+          <t>notable_composition</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Century Of Composers</t>
+          <t>What is a notable composition of the composer?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>musical_composition</t>
+          <t>musical_composition_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Musical Composition</t>
+          <t>What is the type of musical composition?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>musical_composition_type</t>
+          <t>teacher_name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Musical Composition Type</t>
+          <t>Who is the teacher of the class or workshop?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>notable_composition</t>
+          <t>teacher_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Notable Composition</t>
+          <t>How can the teacher be contacted?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>notable_composition_venue</t>
+          <t>class_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Notable Composition Venue</t>
+          <t>When is the class or workshop held?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>notable_composition_venue_type</t>
+          <t>class_location</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Notable Composition Venue Type</t>
+          <t>Where is the class or workshop located?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>teacher_name</t>
+          <t>class_description</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Teacher Name</t>
+          <t>Can we have a list of all compositions of the composer?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>teacher_email</t>
+          <t>class_type</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Teacher Email</t>
+          <t>What type is the class or workshop?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>teacher_phone</t>
+          <t>class_start_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Teacher Phone</t>
+          <t>What is the class or workshop start time?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>class_or_workshop</t>
+          <t>class_end_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Class Or Workshop</t>
+          <t>What is the class or workshop end time?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,297 +791,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>class_or_workshop_date</t>
+          <t>class_notes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Class Or Workshop Date</t>
+          <t>Class Notes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>class_or_workshop_start_time</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Class Or Workshop Start Time</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>class_or_workshop_end_time</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Class Or Workshop End Time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>class_or_workshop_location</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Class Or Workshop Location</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>class_or_workshop_number</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Class Or Workshop Number</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>class_or_workshop_comments</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Class Or Workshop Comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>class_or_workshop</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Class Or Workshop</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>class_or_workshop</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Class Or Workshop</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>class_or_workshop</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Class Or Workshop</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>class_or_workshop</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Class Or Workshop</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>class_or_workshop</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Class Or Workshop</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>class_or_workshop</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Class Or Workshop</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>class_or_workshop</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Class Or Workshop</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,323 +850,323 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20th</t>
+          <t>18th</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20th</t>
+          <t>18th</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19th</t>
+          <t>17th</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19th</t>
+          <t>17th</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18th</t>
+          <t>16th</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18th</t>
+          <t>16th</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17th</t>
+          <t>15th</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17th</t>
+          <t>15th</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16th</t>
+          <t>14th</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16th</t>
+          <t>14th</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15th</t>
+          <t>13th</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15th</t>
+          <t>13th</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14th</t>
+          <t>12th</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14th</t>
+          <t>12th</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13th</t>
+          <t>11th</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13th</t>
+          <t>11th</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12th</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12th</t>
+          <t>10th</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11th</t>
+          <t>9th</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11th</t>
+          <t>9th</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>8th</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>7th</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>6th</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>5th</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>2nd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>composer_century_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>century_of_composers_choices</t>
+          <t>musical_composition_type_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>classical</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>classical</t>
+          <t>folk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>classical</t>
+          <t>folk</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>folk</t>
+          <t>popular</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>folk</t>
+          <t>popular</t>
         </is>
       </c>
     </row>
@@ -1488,146 +1212,44 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>popular</t>
+          <t>experimental</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>popular</t>
+          <t>experimental</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>musical_composition_type_choices</t>
+          <t>class_type_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>experimental</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>experimental</t>
+          <t>online</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>notable_composition_venue_type_choices</t>
+          <t>class_type_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>classical</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>classical</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>notable_composition_venue_type_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>contemporary</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>contemporary</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>notable_composition_venue_type_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>folk</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>folk</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>notable_composition_venue_type_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>popular</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>popular</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>notable_composition_venue_type_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>experimental</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>experimental</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>class_or_workshop_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>class_or_workshop_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>offline</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>offline</t>
         </is>
